--- a/server/templates/quote.xlsx
+++ b/server/templates/quote.xlsx
@@ -11,7 +11,7 @@
     <sheet name="당진 한라 비발디 안전 스위치 " sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'당진 한라 비발디 안전 스위치 '!$A$1:$H$47</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'당진 한라 비발디 안전 스위치 '!$A$1:$H$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -2370,13 +2370,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>704880</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>57240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>133200</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5668,61 +5668,945 @@
       <c r="HT30" s="25"/>
       <c r="HU30" s="25"/>
     </row>
-    <row r="31" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="72" t="s">
-        <v>41</v>
+    <row r="31" s="3" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1"/>
+      <c r="B31" s="75" t="s">
+        <v>45</v>
       </c>
-      <c r="C31" s="25"/>
+      <c r="C31" s="76"/>
       <c r="D31" s="25"/>
       <c r="E31" s="25"/>
       <c r="F31" s="69"/>
       <c r="G31" s="70"/>
       <c r="H31" s="25"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+      <c r="AG31" s="1"/>
+      <c r="AH31" s="1"/>
+      <c r="AI31" s="1"/>
+      <c r="AJ31" s="1"/>
+      <c r="AK31" s="1"/>
+      <c r="AL31" s="1"/>
+      <c r="AM31" s="1"/>
+      <c r="AN31" s="1"/>
+      <c r="AO31" s="1"/>
+      <c r="AP31" s="1"/>
+      <c r="AQ31" s="1"/>
+      <c r="AR31" s="1"/>
+      <c r="AS31" s="1"/>
+      <c r="AT31" s="1"/>
+      <c r="AU31" s="1"/>
+      <c r="AV31" s="1"/>
+      <c r="AW31" s="1"/>
+      <c r="AX31" s="1"/>
+      <c r="AY31" s="1"/>
+      <c r="AZ31" s="1"/>
+      <c r="BA31" s="1"/>
+      <c r="BB31" s="1"/>
+      <c r="BC31" s="1"/>
+      <c r="BD31" s="1"/>
+      <c r="BE31" s="1"/>
+      <c r="BF31" s="1"/>
+      <c r="BG31" s="1"/>
+      <c r="BH31" s="1"/>
+      <c r="BI31" s="1"/>
+      <c r="BJ31" s="1"/>
+      <c r="BK31" s="1"/>
+      <c r="BL31" s="1"/>
+      <c r="BM31" s="1"/>
+      <c r="BN31" s="1"/>
+      <c r="BO31" s="1"/>
+      <c r="BP31" s="1"/>
+      <c r="BQ31" s="1"/>
+      <c r="BR31" s="1"/>
+      <c r="BS31" s="1"/>
+      <c r="BT31" s="1"/>
+      <c r="BU31" s="1"/>
+      <c r="BV31" s="1"/>
+      <c r="BW31" s="1"/>
+      <c r="BX31" s="1"/>
+      <c r="BY31" s="1"/>
+      <c r="BZ31" s="1"/>
+      <c r="CA31" s="1"/>
+      <c r="CB31" s="1"/>
+      <c r="CC31" s="1"/>
+      <c r="CD31" s="1"/>
+      <c r="CE31" s="1"/>
+      <c r="CF31" s="1"/>
+      <c r="CG31" s="1"/>
+      <c r="CH31" s="1"/>
+      <c r="CI31" s="1"/>
+      <c r="CJ31" s="1"/>
+      <c r="CK31" s="1"/>
+      <c r="CL31" s="1"/>
+      <c r="CM31" s="1"/>
+      <c r="CN31" s="1"/>
+      <c r="CO31" s="1"/>
+      <c r="CP31" s="1"/>
+      <c r="CQ31" s="1"/>
+      <c r="CR31" s="1"/>
+      <c r="CS31" s="1"/>
+      <c r="CT31" s="1"/>
+      <c r="CU31" s="1"/>
+      <c r="CV31" s="1"/>
+      <c r="CW31" s="1"/>
+      <c r="CX31" s="1"/>
+      <c r="CY31" s="1"/>
+      <c r="CZ31" s="1"/>
+      <c r="DA31" s="1"/>
+      <c r="DB31" s="1"/>
+      <c r="DC31" s="1"/>
+      <c r="DD31" s="1"/>
+      <c r="DE31" s="1"/>
+      <c r="DF31" s="1"/>
+      <c r="DG31" s="1"/>
+      <c r="DH31" s="1"/>
+      <c r="DI31" s="1"/>
+      <c r="DJ31" s="1"/>
+      <c r="DK31" s="1"/>
+      <c r="DL31" s="1"/>
+      <c r="DM31" s="1"/>
+      <c r="DN31" s="1"/>
+      <c r="DO31" s="1"/>
+      <c r="DP31" s="1"/>
+      <c r="DQ31" s="1"/>
+      <c r="DR31" s="1"/>
+      <c r="DS31" s="1"/>
+      <c r="DT31" s="1"/>
+      <c r="DU31" s="1"/>
+      <c r="DV31" s="1"/>
+      <c r="DW31" s="1"/>
+      <c r="DX31" s="1"/>
+      <c r="DY31" s="1"/>
+      <c r="DZ31" s="1"/>
+      <c r="EA31" s="1"/>
+      <c r="EB31" s="1"/>
+      <c r="EC31" s="1"/>
+      <c r="ED31" s="1"/>
+      <c r="EE31" s="1"/>
+      <c r="EF31" s="1"/>
+      <c r="EG31" s="1"/>
+      <c r="EH31" s="1"/>
+      <c r="EI31" s="1"/>
+      <c r="EJ31" s="1"/>
+      <c r="EK31" s="1"/>
+      <c r="EL31" s="1"/>
+      <c r="EM31" s="1"/>
+      <c r="EN31" s="1"/>
+      <c r="EO31" s="1"/>
+      <c r="EP31" s="1"/>
+      <c r="EQ31" s="1"/>
+      <c r="ER31" s="1"/>
+      <c r="ES31" s="1"/>
+      <c r="ET31" s="1"/>
+      <c r="EU31" s="1"/>
+      <c r="EV31" s="1"/>
+      <c r="EW31" s="1"/>
+      <c r="EX31" s="1"/>
+      <c r="EY31" s="1"/>
+      <c r="EZ31" s="1"/>
+      <c r="FA31" s="1"/>
+      <c r="FB31" s="1"/>
+      <c r="FC31" s="1"/>
+      <c r="FD31" s="1"/>
+      <c r="FE31" s="1"/>
+      <c r="FF31" s="1"/>
+      <c r="FG31" s="1"/>
+      <c r="FH31" s="1"/>
+      <c r="FI31" s="1"/>
+      <c r="FJ31" s="1"/>
+      <c r="FK31" s="1"/>
+      <c r="FL31" s="1"/>
+      <c r="FM31" s="1"/>
+      <c r="FN31" s="1"/>
+      <c r="FO31" s="1"/>
+      <c r="FP31" s="1"/>
+      <c r="FQ31" s="1"/>
+      <c r="FR31" s="1"/>
+      <c r="FS31" s="1"/>
+      <c r="FT31" s="1"/>
+      <c r="FU31" s="1"/>
+      <c r="FV31" s="1"/>
+      <c r="FW31" s="1"/>
+      <c r="FX31" s="1"/>
+      <c r="FY31" s="1"/>
+      <c r="FZ31" s="1"/>
+      <c r="GA31" s="1"/>
+      <c r="GB31" s="1"/>
+      <c r="GC31" s="1"/>
+      <c r="GD31" s="1"/>
+      <c r="GE31" s="1"/>
+      <c r="GF31" s="1"/>
+      <c r="GG31" s="1"/>
+      <c r="GH31" s="1"/>
+      <c r="GI31" s="1"/>
+      <c r="GJ31" s="1"/>
+      <c r="GK31" s="1"/>
+      <c r="GL31" s="1"/>
+      <c r="GM31" s="1"/>
+      <c r="GN31" s="1"/>
+      <c r="GO31" s="1"/>
+      <c r="GP31" s="1"/>
+      <c r="GQ31" s="1"/>
+      <c r="GR31" s="1"/>
+      <c r="GS31" s="1"/>
+      <c r="GT31" s="1"/>
+      <c r="GU31" s="1"/>
+      <c r="GV31" s="1"/>
+      <c r="GW31" s="1"/>
+      <c r="GX31" s="1"/>
+      <c r="GY31" s="1"/>
+      <c r="GZ31" s="1"/>
+      <c r="HA31" s="1"/>
+      <c r="HB31" s="1"/>
+      <c r="HC31" s="1"/>
+      <c r="HD31" s="1"/>
+      <c r="HE31" s="1"/>
+      <c r="HF31" s="1"/>
+      <c r="HG31" s="1"/>
+      <c r="HH31" s="1"/>
+      <c r="HI31" s="1"/>
+      <c r="HJ31" s="1"/>
+      <c r="HK31" s="1"/>
+      <c r="HL31" s="1"/>
+      <c r="HM31" s="1"/>
+      <c r="HN31" s="1"/>
+      <c r="HO31" s="1"/>
+      <c r="HP31" s="1"/>
+      <c r="HQ31" s="1"/>
+      <c r="HR31" s="1"/>
+      <c r="HS31" s="1"/>
+      <c r="HT31" s="1"/>
+      <c r="HU31" s="1"/>
     </row>
-    <row r="32" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="72" t="s">
-        <v>42</v>
+    <row r="32" s="3" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1"/>
+      <c r="B32" s="77" t="s">
+        <v>46</v>
       </c>
-      <c r="C32" s="25"/>
+      <c r="C32" s="76"/>
       <c r="D32" s="25"/>
       <c r="E32" s="25"/>
       <c r="F32" s="69"/>
       <c r="G32" s="70"/>
       <c r="H32" s="25"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1"/>
+      <c r="AG32" s="1"/>
+      <c r="AH32" s="1"/>
+      <c r="AI32" s="1"/>
+      <c r="AJ32" s="1"/>
+      <c r="AK32" s="1"/>
+      <c r="AL32" s="1"/>
+      <c r="AM32" s="1"/>
+      <c r="AN32" s="1"/>
+      <c r="AO32" s="1"/>
+      <c r="AP32" s="1"/>
+      <c r="AQ32" s="1"/>
+      <c r="AR32" s="1"/>
+      <c r="AS32" s="1"/>
+      <c r="AT32" s="1"/>
+      <c r="AU32" s="1"/>
+      <c r="AV32" s="1"/>
+      <c r="AW32" s="1"/>
+      <c r="AX32" s="1"/>
+      <c r="AY32" s="1"/>
+      <c r="AZ32" s="1"/>
+      <c r="BA32" s="1"/>
+      <c r="BB32" s="1"/>
+      <c r="BC32" s="1"/>
+      <c r="BD32" s="1"/>
+      <c r="BE32" s="1"/>
+      <c r="BF32" s="1"/>
+      <c r="BG32" s="1"/>
+      <c r="BH32" s="1"/>
+      <c r="BI32" s="1"/>
+      <c r="BJ32" s="1"/>
+      <c r="BK32" s="1"/>
+      <c r="BL32" s="1"/>
+      <c r="BM32" s="1"/>
+      <c r="BN32" s="1"/>
+      <c r="BO32" s="1"/>
+      <c r="BP32" s="1"/>
+      <c r="BQ32" s="1"/>
+      <c r="BR32" s="1"/>
+      <c r="BS32" s="1"/>
+      <c r="BT32" s="1"/>
+      <c r="BU32" s="1"/>
+      <c r="BV32" s="1"/>
+      <c r="BW32" s="1"/>
+      <c r="BX32" s="1"/>
+      <c r="BY32" s="1"/>
+      <c r="BZ32" s="1"/>
+      <c r="CA32" s="1"/>
+      <c r="CB32" s="1"/>
+      <c r="CC32" s="1"/>
+      <c r="CD32" s="1"/>
+      <c r="CE32" s="1"/>
+      <c r="CF32" s="1"/>
+      <c r="CG32" s="1"/>
+      <c r="CH32" s="1"/>
+      <c r="CI32" s="1"/>
+      <c r="CJ32" s="1"/>
+      <c r="CK32" s="1"/>
+      <c r="CL32" s="1"/>
+      <c r="CM32" s="1"/>
+      <c r="CN32" s="1"/>
+      <c r="CO32" s="1"/>
+      <c r="CP32" s="1"/>
+      <c r="CQ32" s="1"/>
+      <c r="CR32" s="1"/>
+      <c r="CS32" s="1"/>
+      <c r="CT32" s="1"/>
+      <c r="CU32" s="1"/>
+      <c r="CV32" s="1"/>
+      <c r="CW32" s="1"/>
+      <c r="CX32" s="1"/>
+      <c r="CY32" s="1"/>
+      <c r="CZ32" s="1"/>
+      <c r="DA32" s="1"/>
+      <c r="DB32" s="1"/>
+      <c r="DC32" s="1"/>
+      <c r="DD32" s="1"/>
+      <c r="DE32" s="1"/>
+      <c r="DF32" s="1"/>
+      <c r="DG32" s="1"/>
+      <c r="DH32" s="1"/>
+      <c r="DI32" s="1"/>
+      <c r="DJ32" s="1"/>
+      <c r="DK32" s="1"/>
+      <c r="DL32" s="1"/>
+      <c r="DM32" s="1"/>
+      <c r="DN32" s="1"/>
+      <c r="DO32" s="1"/>
+      <c r="DP32" s="1"/>
+      <c r="DQ32" s="1"/>
+      <c r="DR32" s="1"/>
+      <c r="DS32" s="1"/>
+      <c r="DT32" s="1"/>
+      <c r="DU32" s="1"/>
+      <c r="DV32" s="1"/>
+      <c r="DW32" s="1"/>
+      <c r="DX32" s="1"/>
+      <c r="DY32" s="1"/>
+      <c r="DZ32" s="1"/>
+      <c r="EA32" s="1"/>
+      <c r="EB32" s="1"/>
+      <c r="EC32" s="1"/>
+      <c r="ED32" s="1"/>
+      <c r="EE32" s="1"/>
+      <c r="EF32" s="1"/>
+      <c r="EG32" s="1"/>
+      <c r="EH32" s="1"/>
+      <c r="EI32" s="1"/>
+      <c r="EJ32" s="1"/>
+      <c r="EK32" s="1"/>
+      <c r="EL32" s="1"/>
+      <c r="EM32" s="1"/>
+      <c r="EN32" s="1"/>
+      <c r="EO32" s="1"/>
+      <c r="EP32" s="1"/>
+      <c r="EQ32" s="1"/>
+      <c r="ER32" s="1"/>
+      <c r="ES32" s="1"/>
+      <c r="ET32" s="1"/>
+      <c r="EU32" s="1"/>
+      <c r="EV32" s="1"/>
+      <c r="EW32" s="1"/>
+      <c r="EX32" s="1"/>
+      <c r="EY32" s="1"/>
+      <c r="EZ32" s="1"/>
+      <c r="FA32" s="1"/>
+      <c r="FB32" s="1"/>
+      <c r="FC32" s="1"/>
+      <c r="FD32" s="1"/>
+      <c r="FE32" s="1"/>
+      <c r="FF32" s="1"/>
+      <c r="FG32" s="1"/>
+      <c r="FH32" s="1"/>
+      <c r="FI32" s="1"/>
+      <c r="FJ32" s="1"/>
+      <c r="FK32" s="1"/>
+      <c r="FL32" s="1"/>
+      <c r="FM32" s="1"/>
+      <c r="FN32" s="1"/>
+      <c r="FO32" s="1"/>
+      <c r="FP32" s="1"/>
+      <c r="FQ32" s="1"/>
+      <c r="FR32" s="1"/>
+      <c r="FS32" s="1"/>
+      <c r="FT32" s="1"/>
+      <c r="FU32" s="1"/>
+      <c r="FV32" s="1"/>
+      <c r="FW32" s="1"/>
+      <c r="FX32" s="1"/>
+      <c r="FY32" s="1"/>
+      <c r="FZ32" s="1"/>
+      <c r="GA32" s="1"/>
+      <c r="GB32" s="1"/>
+      <c r="GC32" s="1"/>
+      <c r="GD32" s="1"/>
+      <c r="GE32" s="1"/>
+      <c r="GF32" s="1"/>
+      <c r="GG32" s="1"/>
+      <c r="GH32" s="1"/>
+      <c r="GI32" s="1"/>
+      <c r="GJ32" s="1"/>
+      <c r="GK32" s="1"/>
+      <c r="GL32" s="1"/>
+      <c r="GM32" s="1"/>
+      <c r="GN32" s="1"/>
+      <c r="GO32" s="1"/>
+      <c r="GP32" s="1"/>
+      <c r="GQ32" s="1"/>
+      <c r="GR32" s="1"/>
+      <c r="GS32" s="1"/>
+      <c r="GT32" s="1"/>
+      <c r="GU32" s="1"/>
+      <c r="GV32" s="1"/>
+      <c r="GW32" s="1"/>
+      <c r="GX32" s="1"/>
+      <c r="GY32" s="1"/>
+      <c r="GZ32" s="1"/>
+      <c r="HA32" s="1"/>
+      <c r="HB32" s="1"/>
+      <c r="HC32" s="1"/>
+      <c r="HD32" s="1"/>
+      <c r="HE32" s="1"/>
+      <c r="HF32" s="1"/>
+      <c r="HG32" s="1"/>
+      <c r="HH32" s="1"/>
+      <c r="HI32" s="1"/>
+      <c r="HJ32" s="1"/>
+      <c r="HK32" s="1"/>
+      <c r="HL32" s="1"/>
+      <c r="HM32" s="1"/>
+      <c r="HN32" s="1"/>
+      <c r="HO32" s="1"/>
+      <c r="HP32" s="1"/>
+      <c r="HQ32" s="1"/>
+      <c r="HR32" s="1"/>
+      <c r="HS32" s="1"/>
+      <c r="HT32" s="1"/>
+      <c r="HU32" s="1"/>
     </row>
-    <row r="33" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="72" t="s">
-        <v>43</v>
+    <row r="33" s="3" customFormat="true" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1"/>
+      <c r="B33" s="78" t="s">
+        <v>47</v>
       </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="25"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1"/>
+      <c r="AD33" s="1"/>
+      <c r="AE33" s="1"/>
+      <c r="AF33" s="1"/>
+      <c r="AG33" s="1"/>
+      <c r="AH33" s="1"/>
+      <c r="AI33" s="1"/>
+      <c r="AJ33" s="1"/>
+      <c r="AK33" s="1"/>
+      <c r="AL33" s="1"/>
+      <c r="AM33" s="1"/>
+      <c r="AN33" s="1"/>
+      <c r="AO33" s="1"/>
+      <c r="AP33" s="1"/>
+      <c r="AQ33" s="1"/>
+      <c r="AR33" s="1"/>
+      <c r="AS33" s="1"/>
+      <c r="AT33" s="1"/>
+      <c r="AU33" s="1"/>
+      <c r="AV33" s="1"/>
+      <c r="AW33" s="1"/>
+      <c r="AX33" s="1"/>
+      <c r="AY33" s="1"/>
+      <c r="AZ33" s="1"/>
+      <c r="BA33" s="1"/>
+      <c r="BB33" s="1"/>
+      <c r="BC33" s="1"/>
+      <c r="BD33" s="1"/>
+      <c r="BE33" s="1"/>
+      <c r="BF33" s="1"/>
+      <c r="BG33" s="1"/>
+      <c r="BH33" s="1"/>
+      <c r="BI33" s="1"/>
+      <c r="BJ33" s="1"/>
+      <c r="BK33" s="1"/>
+      <c r="BL33" s="1"/>
+      <c r="BM33" s="1"/>
+      <c r="BN33" s="1"/>
+      <c r="BO33" s="1"/>
+      <c r="BP33" s="1"/>
+      <c r="BQ33" s="1"/>
+      <c r="BR33" s="1"/>
+      <c r="BS33" s="1"/>
+      <c r="BT33" s="1"/>
+      <c r="BU33" s="1"/>
+      <c r="BV33" s="1"/>
+      <c r="BW33" s="1"/>
+      <c r="BX33" s="1"/>
+      <c r="BY33" s="1"/>
+      <c r="BZ33" s="1"/>
+      <c r="CA33" s="1"/>
+      <c r="CB33" s="1"/>
+      <c r="CC33" s="1"/>
+      <c r="CD33" s="1"/>
+      <c r="CE33" s="1"/>
+      <c r="CF33" s="1"/>
+      <c r="CG33" s="1"/>
+      <c r="CH33" s="1"/>
+      <c r="CI33" s="1"/>
+      <c r="CJ33" s="1"/>
+      <c r="CK33" s="1"/>
+      <c r="CL33" s="1"/>
+      <c r="CM33" s="1"/>
+      <c r="CN33" s="1"/>
+      <c r="CO33" s="1"/>
+      <c r="CP33" s="1"/>
+      <c r="CQ33" s="1"/>
+      <c r="CR33" s="1"/>
+      <c r="CS33" s="1"/>
+      <c r="CT33" s="1"/>
+      <c r="CU33" s="1"/>
+      <c r="CV33" s="1"/>
+      <c r="CW33" s="1"/>
+      <c r="CX33" s="1"/>
+      <c r="CY33" s="1"/>
+      <c r="CZ33" s="1"/>
+      <c r="DA33" s="1"/>
+      <c r="DB33" s="1"/>
+      <c r="DC33" s="1"/>
+      <c r="DD33" s="1"/>
+      <c r="DE33" s="1"/>
+      <c r="DF33" s="1"/>
+      <c r="DG33" s="1"/>
+      <c r="DH33" s="1"/>
+      <c r="DI33" s="1"/>
+      <c r="DJ33" s="1"/>
+      <c r="DK33" s="1"/>
+      <c r="DL33" s="1"/>
+      <c r="DM33" s="1"/>
+      <c r="DN33" s="1"/>
+      <c r="DO33" s="1"/>
+      <c r="DP33" s="1"/>
+      <c r="DQ33" s="1"/>
+      <c r="DR33" s="1"/>
+      <c r="DS33" s="1"/>
+      <c r="DT33" s="1"/>
+      <c r="DU33" s="1"/>
+      <c r="DV33" s="1"/>
+      <c r="DW33" s="1"/>
+      <c r="DX33" s="1"/>
+      <c r="DY33" s="1"/>
+      <c r="DZ33" s="1"/>
+      <c r="EA33" s="1"/>
+      <c r="EB33" s="1"/>
+      <c r="EC33" s="1"/>
+      <c r="ED33" s="1"/>
+      <c r="EE33" s="1"/>
+      <c r="EF33" s="1"/>
+      <c r="EG33" s="1"/>
+      <c r="EH33" s="1"/>
+      <c r="EI33" s="1"/>
+      <c r="EJ33" s="1"/>
+      <c r="EK33" s="1"/>
+      <c r="EL33" s="1"/>
+      <c r="EM33" s="1"/>
+      <c r="EN33" s="1"/>
+      <c r="EO33" s="1"/>
+      <c r="EP33" s="1"/>
+      <c r="EQ33" s="1"/>
+      <c r="ER33" s="1"/>
+      <c r="ES33" s="1"/>
+      <c r="ET33" s="1"/>
+      <c r="EU33" s="1"/>
+      <c r="EV33" s="1"/>
+      <c r="EW33" s="1"/>
+      <c r="EX33" s="1"/>
+      <c r="EY33" s="1"/>
+      <c r="EZ33" s="1"/>
+      <c r="FA33" s="1"/>
+      <c r="FB33" s="1"/>
+      <c r="FC33" s="1"/>
+      <c r="FD33" s="1"/>
+      <c r="FE33" s="1"/>
+      <c r="FF33" s="1"/>
+      <c r="FG33" s="1"/>
+      <c r="FH33" s="1"/>
+      <c r="FI33" s="1"/>
+      <c r="FJ33" s="1"/>
+      <c r="FK33" s="1"/>
+      <c r="FL33" s="1"/>
+      <c r="FM33" s="1"/>
+      <c r="FN33" s="1"/>
+      <c r="FO33" s="1"/>
+      <c r="FP33" s="1"/>
+      <c r="FQ33" s="1"/>
+      <c r="FR33" s="1"/>
+      <c r="FS33" s="1"/>
+      <c r="FT33" s="1"/>
+      <c r="FU33" s="1"/>
+      <c r="FV33" s="1"/>
+      <c r="FW33" s="1"/>
+      <c r="FX33" s="1"/>
+      <c r="FY33" s="1"/>
+      <c r="FZ33" s="1"/>
+      <c r="GA33" s="1"/>
+      <c r="GB33" s="1"/>
+      <c r="GC33" s="1"/>
+      <c r="GD33" s="1"/>
+      <c r="GE33" s="1"/>
+      <c r="GF33" s="1"/>
+      <c r="GG33" s="1"/>
+      <c r="GH33" s="1"/>
+      <c r="GI33" s="1"/>
+      <c r="GJ33" s="1"/>
+      <c r="GK33" s="1"/>
+      <c r="GL33" s="1"/>
+      <c r="GM33" s="1"/>
+      <c r="GN33" s="1"/>
+      <c r="GO33" s="1"/>
+      <c r="GP33" s="1"/>
+      <c r="GQ33" s="1"/>
+      <c r="GR33" s="1"/>
+      <c r="GS33" s="1"/>
+      <c r="GT33" s="1"/>
+      <c r="GU33" s="1"/>
+      <c r="GV33" s="1"/>
+      <c r="GW33" s="1"/>
+      <c r="GX33" s="1"/>
+      <c r="GY33" s="1"/>
+      <c r="GZ33" s="1"/>
+      <c r="HA33" s="1"/>
+      <c r="HB33" s="1"/>
+      <c r="HC33" s="1"/>
+      <c r="HD33" s="1"/>
+      <c r="HE33" s="1"/>
+      <c r="HF33" s="1"/>
+      <c r="HG33" s="1"/>
+      <c r="HH33" s="1"/>
+      <c r="HI33" s="1"/>
+      <c r="HJ33" s="1"/>
+      <c r="HK33" s="1"/>
+      <c r="HL33" s="1"/>
+      <c r="HM33" s="1"/>
+      <c r="HN33" s="1"/>
+      <c r="HO33" s="1"/>
+      <c r="HP33" s="1"/>
+      <c r="HQ33" s="1"/>
+      <c r="HR33" s="1"/>
+      <c r="HS33" s="1"/>
+      <c r="HT33" s="1"/>
+      <c r="HU33" s="1"/>
     </row>
-    <row r="34" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="72" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="25"/>
+    <row r="34" s="3" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1"/>
+      <c r="B34" s="84"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="85"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
+      <c r="AD34" s="1"/>
+      <c r="AE34" s="1"/>
+      <c r="AF34" s="1"/>
+      <c r="AG34" s="1"/>
+      <c r="AH34" s="1"/>
+      <c r="AI34" s="1"/>
+      <c r="AJ34" s="1"/>
+      <c r="AK34" s="1"/>
+      <c r="AL34" s="1"/>
+      <c r="AM34" s="1"/>
+      <c r="AN34" s="1"/>
+      <c r="AO34" s="1"/>
+      <c r="AP34" s="1"/>
+      <c r="AQ34" s="1"/>
+      <c r="AR34" s="1"/>
+      <c r="AS34" s="1"/>
+      <c r="AT34" s="1"/>
+      <c r="AU34" s="1"/>
+      <c r="AV34" s="1"/>
+      <c r="AW34" s="1"/>
+      <c r="AX34" s="1"/>
+      <c r="AY34" s="1"/>
+      <c r="AZ34" s="1"/>
+      <c r="BA34" s="1"/>
+      <c r="BB34" s="1"/>
+      <c r="BC34" s="1"/>
+      <c r="BD34" s="1"/>
+      <c r="BE34" s="1"/>
+      <c r="BF34" s="1"/>
+      <c r="BG34" s="1"/>
+      <c r="BH34" s="1"/>
+      <c r="BI34" s="1"/>
+      <c r="BJ34" s="1"/>
+      <c r="BK34" s="1"/>
+      <c r="BL34" s="1"/>
+      <c r="BM34" s="1"/>
+      <c r="BN34" s="1"/>
+      <c r="BO34" s="1"/>
+      <c r="BP34" s="1"/>
+      <c r="BQ34" s="1"/>
+      <c r="BR34" s="1"/>
+      <c r="BS34" s="1"/>
+      <c r="BT34" s="1"/>
+      <c r="BU34" s="1"/>
+      <c r="BV34" s="1"/>
+      <c r="BW34" s="1"/>
+      <c r="BX34" s="1"/>
+      <c r="BY34" s="1"/>
+      <c r="BZ34" s="1"/>
+      <c r="CA34" s="1"/>
+      <c r="CB34" s="1"/>
+      <c r="CC34" s="1"/>
+      <c r="CD34" s="1"/>
+      <c r="CE34" s="1"/>
+      <c r="CF34" s="1"/>
+      <c r="CG34" s="1"/>
+      <c r="CH34" s="1"/>
+      <c r="CI34" s="1"/>
+      <c r="CJ34" s="1"/>
+      <c r="CK34" s="1"/>
+      <c r="CL34" s="1"/>
+      <c r="CM34" s="1"/>
+      <c r="CN34" s="1"/>
+      <c r="CO34" s="1"/>
+      <c r="CP34" s="1"/>
+      <c r="CQ34" s="1"/>
+      <c r="CR34" s="1"/>
+      <c r="CS34" s="1"/>
+      <c r="CT34" s="1"/>
+      <c r="CU34" s="1"/>
+      <c r="CV34" s="1"/>
+      <c r="CW34" s="1"/>
+      <c r="CX34" s="1"/>
+      <c r="CY34" s="1"/>
+      <c r="CZ34" s="1"/>
+      <c r="DA34" s="1"/>
+      <c r="DB34" s="1"/>
+      <c r="DC34" s="1"/>
+      <c r="DD34" s="1"/>
+      <c r="DE34" s="1"/>
+      <c r="DF34" s="1"/>
+      <c r="DG34" s="1"/>
+      <c r="DH34" s="1"/>
+      <c r="DI34" s="1"/>
+      <c r="DJ34" s="1"/>
+      <c r="DK34" s="1"/>
+      <c r="DL34" s="1"/>
+      <c r="DM34" s="1"/>
+      <c r="DN34" s="1"/>
+      <c r="DO34" s="1"/>
+      <c r="DP34" s="1"/>
+      <c r="DQ34" s="1"/>
+      <c r="DR34" s="1"/>
+      <c r="DS34" s="1"/>
+      <c r="DT34" s="1"/>
+      <c r="DU34" s="1"/>
+      <c r="DV34" s="1"/>
+      <c r="DW34" s="1"/>
+      <c r="DX34" s="1"/>
+      <c r="DY34" s="1"/>
+      <c r="DZ34" s="1"/>
+      <c r="EA34" s="1"/>
+      <c r="EB34" s="1"/>
+      <c r="EC34" s="1"/>
+      <c r="ED34" s="1"/>
+      <c r="EE34" s="1"/>
+      <c r="EF34" s="1"/>
+      <c r="EG34" s="1"/>
+      <c r="EH34" s="1"/>
+      <c r="EI34" s="1"/>
+      <c r="EJ34" s="1"/>
+      <c r="EK34" s="1"/>
+      <c r="EL34" s="1"/>
+      <c r="EM34" s="1"/>
+      <c r="EN34" s="1"/>
+      <c r="EO34" s="1"/>
+      <c r="EP34" s="1"/>
+      <c r="EQ34" s="1"/>
+      <c r="ER34" s="1"/>
+      <c r="ES34" s="1"/>
+      <c r="ET34" s="1"/>
+      <c r="EU34" s="1"/>
+      <c r="EV34" s="1"/>
+      <c r="EW34" s="1"/>
+      <c r="EX34" s="1"/>
+      <c r="EY34" s="1"/>
+      <c r="EZ34" s="1"/>
+      <c r="FA34" s="1"/>
+      <c r="FB34" s="1"/>
+      <c r="FC34" s="1"/>
+      <c r="FD34" s="1"/>
+      <c r="FE34" s="1"/>
+      <c r="FF34" s="1"/>
+      <c r="FG34" s="1"/>
+      <c r="FH34" s="1"/>
+      <c r="FI34" s="1"/>
+      <c r="FJ34" s="1"/>
+      <c r="FK34" s="1"/>
+      <c r="FL34" s="1"/>
+      <c r="FM34" s="1"/>
+      <c r="FN34" s="1"/>
+      <c r="FO34" s="1"/>
+      <c r="FP34" s="1"/>
+      <c r="FQ34" s="1"/>
+      <c r="FR34" s="1"/>
+      <c r="FS34" s="1"/>
+      <c r="FT34" s="1"/>
+      <c r="FU34" s="1"/>
+      <c r="FV34" s="1"/>
+      <c r="FW34" s="1"/>
+      <c r="FX34" s="1"/>
+      <c r="FY34" s="1"/>
+      <c r="FZ34" s="1"/>
+      <c r="GA34" s="1"/>
+      <c r="GB34" s="1"/>
+      <c r="GC34" s="1"/>
+      <c r="GD34" s="1"/>
+      <c r="GE34" s="1"/>
+      <c r="GF34" s="1"/>
+      <c r="GG34" s="1"/>
+      <c r="GH34" s="1"/>
+      <c r="GI34" s="1"/>
+      <c r="GJ34" s="1"/>
+      <c r="GK34" s="1"/>
+      <c r="GL34" s="1"/>
+      <c r="GM34" s="1"/>
+      <c r="GN34" s="1"/>
+      <c r="GO34" s="1"/>
+      <c r="GP34" s="1"/>
+      <c r="GQ34" s="1"/>
+      <c r="GR34" s="1"/>
+      <c r="GS34" s="1"/>
+      <c r="GT34" s="1"/>
+      <c r="GU34" s="1"/>
+      <c r="GV34" s="1"/>
+      <c r="GW34" s="1"/>
+      <c r="GX34" s="1"/>
+      <c r="GY34" s="1"/>
+      <c r="GZ34" s="1"/>
+      <c r="HA34" s="1"/>
+      <c r="HB34" s="1"/>
+      <c r="HC34" s="1"/>
+      <c r="HD34" s="1"/>
+      <c r="HE34" s="1"/>
+      <c r="HF34" s="1"/>
+      <c r="HG34" s="1"/>
+      <c r="HH34" s="1"/>
+      <c r="HI34" s="1"/>
+      <c r="HJ34" s="1"/>
+      <c r="HK34" s="1"/>
+      <c r="HL34" s="1"/>
+      <c r="HM34" s="1"/>
+      <c r="HN34" s="1"/>
+      <c r="HO34" s="1"/>
+      <c r="HP34" s="1"/>
+      <c r="HQ34" s="1"/>
+      <c r="HR34" s="1"/>
+      <c r="HS34" s="1"/>
+      <c r="HT34" s="1"/>
+      <c r="HU34" s="1"/>
     </row>
     <row r="35" s="3" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1"/>
-      <c r="B35" s="75" t="s">
-        <v>45</v>
+      <c r="B35" s="86" t="s">
+        <v>48</v>
       </c>
-      <c r="C35" s="76"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="25"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="85"/>
       <c r="I35" s="6"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -5947,15 +6831,12 @@
     </row>
     <row r="36" s="3" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1"/>
-      <c r="B36" s="77" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="76"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="25"/>
+      <c r="B36" s="84"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="85"/>
       <c r="I36" s="6"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -6178,17 +7059,16 @@
       <c r="HT36" s="1"/>
       <c r="HU36" s="1"/>
     </row>
-    <row r="37" s="3" customFormat="true" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" s="3" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1"/>
-      <c r="B37" s="78" t="s">
-        <v>47</v>
+      <c r="B37" s="86" t="s">
+        <v>49</v>
       </c>
-      <c r="C37" s="79"/>
-      <c r="D37" s="80"/>
-      <c r="E37" s="80"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="82"/>
-      <c r="H37" s="83"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="85"/>
       <c r="I37" s="6"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -6644,7 +7524,7 @@
     <row r="39" s="3" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1"/>
       <c r="B39" s="86" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -6875,12 +7755,13 @@
     </row>
     <row r="40" s="3" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1"/>
-      <c r="B40" s="84"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="85"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="88"/>
+      <c r="D40" s="89"/>
+      <c r="E40" s="89"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="92"/>
       <c r="I40" s="6"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -7103,931 +7984,6 @@
       <c r="HT40" s="1"/>
       <c r="HU40" s="1"/>
     </row>
-    <row r="41" s="3" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1"/>
-      <c r="B41" s="86" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="85"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
-      <c r="W41" s="1"/>
-      <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
-      <c r="Z41" s="1"/>
-      <c r="AA41" s="1"/>
-      <c r="AB41" s="1"/>
-      <c r="AC41" s="1"/>
-      <c r="AD41" s="1"/>
-      <c r="AE41" s="1"/>
-      <c r="AF41" s="1"/>
-      <c r="AG41" s="1"/>
-      <c r="AH41" s="1"/>
-      <c r="AI41" s="1"/>
-      <c r="AJ41" s="1"/>
-      <c r="AK41" s="1"/>
-      <c r="AL41" s="1"/>
-      <c r="AM41" s="1"/>
-      <c r="AN41" s="1"/>
-      <c r="AO41" s="1"/>
-      <c r="AP41" s="1"/>
-      <c r="AQ41" s="1"/>
-      <c r="AR41" s="1"/>
-      <c r="AS41" s="1"/>
-      <c r="AT41" s="1"/>
-      <c r="AU41" s="1"/>
-      <c r="AV41" s="1"/>
-      <c r="AW41" s="1"/>
-      <c r="AX41" s="1"/>
-      <c r="AY41" s="1"/>
-      <c r="AZ41" s="1"/>
-      <c r="BA41" s="1"/>
-      <c r="BB41" s="1"/>
-      <c r="BC41" s="1"/>
-      <c r="BD41" s="1"/>
-      <c r="BE41" s="1"/>
-      <c r="BF41" s="1"/>
-      <c r="BG41" s="1"/>
-      <c r="BH41" s="1"/>
-      <c r="BI41" s="1"/>
-      <c r="BJ41" s="1"/>
-      <c r="BK41" s="1"/>
-      <c r="BL41" s="1"/>
-      <c r="BM41" s="1"/>
-      <c r="BN41" s="1"/>
-      <c r="BO41" s="1"/>
-      <c r="BP41" s="1"/>
-      <c r="BQ41" s="1"/>
-      <c r="BR41" s="1"/>
-      <c r="BS41" s="1"/>
-      <c r="BT41" s="1"/>
-      <c r="BU41" s="1"/>
-      <c r="BV41" s="1"/>
-      <c r="BW41" s="1"/>
-      <c r="BX41" s="1"/>
-      <c r="BY41" s="1"/>
-      <c r="BZ41" s="1"/>
-      <c r="CA41" s="1"/>
-      <c r="CB41" s="1"/>
-      <c r="CC41" s="1"/>
-      <c r="CD41" s="1"/>
-      <c r="CE41" s="1"/>
-      <c r="CF41" s="1"/>
-      <c r="CG41" s="1"/>
-      <c r="CH41" s="1"/>
-      <c r="CI41" s="1"/>
-      <c r="CJ41" s="1"/>
-      <c r="CK41" s="1"/>
-      <c r="CL41" s="1"/>
-      <c r="CM41" s="1"/>
-      <c r="CN41" s="1"/>
-      <c r="CO41" s="1"/>
-      <c r="CP41" s="1"/>
-      <c r="CQ41" s="1"/>
-      <c r="CR41" s="1"/>
-      <c r="CS41" s="1"/>
-      <c r="CT41" s="1"/>
-      <c r="CU41" s="1"/>
-      <c r="CV41" s="1"/>
-      <c r="CW41" s="1"/>
-      <c r="CX41" s="1"/>
-      <c r="CY41" s="1"/>
-      <c r="CZ41" s="1"/>
-      <c r="DA41" s="1"/>
-      <c r="DB41" s="1"/>
-      <c r="DC41" s="1"/>
-      <c r="DD41" s="1"/>
-      <c r="DE41" s="1"/>
-      <c r="DF41" s="1"/>
-      <c r="DG41" s="1"/>
-      <c r="DH41" s="1"/>
-      <c r="DI41" s="1"/>
-      <c r="DJ41" s="1"/>
-      <c r="DK41" s="1"/>
-      <c r="DL41" s="1"/>
-      <c r="DM41" s="1"/>
-      <c r="DN41" s="1"/>
-      <c r="DO41" s="1"/>
-      <c r="DP41" s="1"/>
-      <c r="DQ41" s="1"/>
-      <c r="DR41" s="1"/>
-      <c r="DS41" s="1"/>
-      <c r="DT41" s="1"/>
-      <c r="DU41" s="1"/>
-      <c r="DV41" s="1"/>
-      <c r="DW41" s="1"/>
-      <c r="DX41" s="1"/>
-      <c r="DY41" s="1"/>
-      <c r="DZ41" s="1"/>
-      <c r="EA41" s="1"/>
-      <c r="EB41" s="1"/>
-      <c r="EC41" s="1"/>
-      <c r="ED41" s="1"/>
-      <c r="EE41" s="1"/>
-      <c r="EF41" s="1"/>
-      <c r="EG41" s="1"/>
-      <c r="EH41" s="1"/>
-      <c r="EI41" s="1"/>
-      <c r="EJ41" s="1"/>
-      <c r="EK41" s="1"/>
-      <c r="EL41" s="1"/>
-      <c r="EM41" s="1"/>
-      <c r="EN41" s="1"/>
-      <c r="EO41" s="1"/>
-      <c r="EP41" s="1"/>
-      <c r="EQ41" s="1"/>
-      <c r="ER41" s="1"/>
-      <c r="ES41" s="1"/>
-      <c r="ET41" s="1"/>
-      <c r="EU41" s="1"/>
-      <c r="EV41" s="1"/>
-      <c r="EW41" s="1"/>
-      <c r="EX41" s="1"/>
-      <c r="EY41" s="1"/>
-      <c r="EZ41" s="1"/>
-      <c r="FA41" s="1"/>
-      <c r="FB41" s="1"/>
-      <c r="FC41" s="1"/>
-      <c r="FD41" s="1"/>
-      <c r="FE41" s="1"/>
-      <c r="FF41" s="1"/>
-      <c r="FG41" s="1"/>
-      <c r="FH41" s="1"/>
-      <c r="FI41" s="1"/>
-      <c r="FJ41" s="1"/>
-      <c r="FK41" s="1"/>
-      <c r="FL41" s="1"/>
-      <c r="FM41" s="1"/>
-      <c r="FN41" s="1"/>
-      <c r="FO41" s="1"/>
-      <c r="FP41" s="1"/>
-      <c r="FQ41" s="1"/>
-      <c r="FR41" s="1"/>
-      <c r="FS41" s="1"/>
-      <c r="FT41" s="1"/>
-      <c r="FU41" s="1"/>
-      <c r="FV41" s="1"/>
-      <c r="FW41" s="1"/>
-      <c r="FX41" s="1"/>
-      <c r="FY41" s="1"/>
-      <c r="FZ41" s="1"/>
-      <c r="GA41" s="1"/>
-      <c r="GB41" s="1"/>
-      <c r="GC41" s="1"/>
-      <c r="GD41" s="1"/>
-      <c r="GE41" s="1"/>
-      <c r="GF41" s="1"/>
-      <c r="GG41" s="1"/>
-      <c r="GH41" s="1"/>
-      <c r="GI41" s="1"/>
-      <c r="GJ41" s="1"/>
-      <c r="GK41" s="1"/>
-      <c r="GL41" s="1"/>
-      <c r="GM41" s="1"/>
-      <c r="GN41" s="1"/>
-      <c r="GO41" s="1"/>
-      <c r="GP41" s="1"/>
-      <c r="GQ41" s="1"/>
-      <c r="GR41" s="1"/>
-      <c r="GS41" s="1"/>
-      <c r="GT41" s="1"/>
-      <c r="GU41" s="1"/>
-      <c r="GV41" s="1"/>
-      <c r="GW41" s="1"/>
-      <c r="GX41" s="1"/>
-      <c r="GY41" s="1"/>
-      <c r="GZ41" s="1"/>
-      <c r="HA41" s="1"/>
-      <c r="HB41" s="1"/>
-      <c r="HC41" s="1"/>
-      <c r="HD41" s="1"/>
-      <c r="HE41" s="1"/>
-      <c r="HF41" s="1"/>
-      <c r="HG41" s="1"/>
-      <c r="HH41" s="1"/>
-      <c r="HI41" s="1"/>
-      <c r="HJ41" s="1"/>
-      <c r="HK41" s="1"/>
-      <c r="HL41" s="1"/>
-      <c r="HM41" s="1"/>
-      <c r="HN41" s="1"/>
-      <c r="HO41" s="1"/>
-      <c r="HP41" s="1"/>
-      <c r="HQ41" s="1"/>
-      <c r="HR41" s="1"/>
-      <c r="HS41" s="1"/>
-      <c r="HT41" s="1"/>
-      <c r="HU41" s="1"/>
-    </row>
-    <row r="42" s="3" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1"/>
-      <c r="B42" s="84"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="85"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1"/>
-      <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
-      <c r="AB42" s="1"/>
-      <c r="AC42" s="1"/>
-      <c r="AD42" s="1"/>
-      <c r="AE42" s="1"/>
-      <c r="AF42" s="1"/>
-      <c r="AG42" s="1"/>
-      <c r="AH42" s="1"/>
-      <c r="AI42" s="1"/>
-      <c r="AJ42" s="1"/>
-      <c r="AK42" s="1"/>
-      <c r="AL42" s="1"/>
-      <c r="AM42" s="1"/>
-      <c r="AN42" s="1"/>
-      <c r="AO42" s="1"/>
-      <c r="AP42" s="1"/>
-      <c r="AQ42" s="1"/>
-      <c r="AR42" s="1"/>
-      <c r="AS42" s="1"/>
-      <c r="AT42" s="1"/>
-      <c r="AU42" s="1"/>
-      <c r="AV42" s="1"/>
-      <c r="AW42" s="1"/>
-      <c r="AX42" s="1"/>
-      <c r="AY42" s="1"/>
-      <c r="AZ42" s="1"/>
-      <c r="BA42" s="1"/>
-      <c r="BB42" s="1"/>
-      <c r="BC42" s="1"/>
-      <c r="BD42" s="1"/>
-      <c r="BE42" s="1"/>
-      <c r="BF42" s="1"/>
-      <c r="BG42" s="1"/>
-      <c r="BH42" s="1"/>
-      <c r="BI42" s="1"/>
-      <c r="BJ42" s="1"/>
-      <c r="BK42" s="1"/>
-      <c r="BL42" s="1"/>
-      <c r="BM42" s="1"/>
-      <c r="BN42" s="1"/>
-      <c r="BO42" s="1"/>
-      <c r="BP42" s="1"/>
-      <c r="BQ42" s="1"/>
-      <c r="BR42" s="1"/>
-      <c r="BS42" s="1"/>
-      <c r="BT42" s="1"/>
-      <c r="BU42" s="1"/>
-      <c r="BV42" s="1"/>
-      <c r="BW42" s="1"/>
-      <c r="BX42" s="1"/>
-      <c r="BY42" s="1"/>
-      <c r="BZ42" s="1"/>
-      <c r="CA42" s="1"/>
-      <c r="CB42" s="1"/>
-      <c r="CC42" s="1"/>
-      <c r="CD42" s="1"/>
-      <c r="CE42" s="1"/>
-      <c r="CF42" s="1"/>
-      <c r="CG42" s="1"/>
-      <c r="CH42" s="1"/>
-      <c r="CI42" s="1"/>
-      <c r="CJ42" s="1"/>
-      <c r="CK42" s="1"/>
-      <c r="CL42" s="1"/>
-      <c r="CM42" s="1"/>
-      <c r="CN42" s="1"/>
-      <c r="CO42" s="1"/>
-      <c r="CP42" s="1"/>
-      <c r="CQ42" s="1"/>
-      <c r="CR42" s="1"/>
-      <c r="CS42" s="1"/>
-      <c r="CT42" s="1"/>
-      <c r="CU42" s="1"/>
-      <c r="CV42" s="1"/>
-      <c r="CW42" s="1"/>
-      <c r="CX42" s="1"/>
-      <c r="CY42" s="1"/>
-      <c r="CZ42" s="1"/>
-      <c r="DA42" s="1"/>
-      <c r="DB42" s="1"/>
-      <c r="DC42" s="1"/>
-      <c r="DD42" s="1"/>
-      <c r="DE42" s="1"/>
-      <c r="DF42" s="1"/>
-      <c r="DG42" s="1"/>
-      <c r="DH42" s="1"/>
-      <c r="DI42" s="1"/>
-      <c r="DJ42" s="1"/>
-      <c r="DK42" s="1"/>
-      <c r="DL42" s="1"/>
-      <c r="DM42" s="1"/>
-      <c r="DN42" s="1"/>
-      <c r="DO42" s="1"/>
-      <c r="DP42" s="1"/>
-      <c r="DQ42" s="1"/>
-      <c r="DR42" s="1"/>
-      <c r="DS42" s="1"/>
-      <c r="DT42" s="1"/>
-      <c r="DU42" s="1"/>
-      <c r="DV42" s="1"/>
-      <c r="DW42" s="1"/>
-      <c r="DX42" s="1"/>
-      <c r="DY42" s="1"/>
-      <c r="DZ42" s="1"/>
-      <c r="EA42" s="1"/>
-      <c r="EB42" s="1"/>
-      <c r="EC42" s="1"/>
-      <c r="ED42" s="1"/>
-      <c r="EE42" s="1"/>
-      <c r="EF42" s="1"/>
-      <c r="EG42" s="1"/>
-      <c r="EH42" s="1"/>
-      <c r="EI42" s="1"/>
-      <c r="EJ42" s="1"/>
-      <c r="EK42" s="1"/>
-      <c r="EL42" s="1"/>
-      <c r="EM42" s="1"/>
-      <c r="EN42" s="1"/>
-      <c r="EO42" s="1"/>
-      <c r="EP42" s="1"/>
-      <c r="EQ42" s="1"/>
-      <c r="ER42" s="1"/>
-      <c r="ES42" s="1"/>
-      <c r="ET42" s="1"/>
-      <c r="EU42" s="1"/>
-      <c r="EV42" s="1"/>
-      <c r="EW42" s="1"/>
-      <c r="EX42" s="1"/>
-      <c r="EY42" s="1"/>
-      <c r="EZ42" s="1"/>
-      <c r="FA42" s="1"/>
-      <c r="FB42" s="1"/>
-      <c r="FC42" s="1"/>
-      <c r="FD42" s="1"/>
-      <c r="FE42" s="1"/>
-      <c r="FF42" s="1"/>
-      <c r="FG42" s="1"/>
-      <c r="FH42" s="1"/>
-      <c r="FI42" s="1"/>
-      <c r="FJ42" s="1"/>
-      <c r="FK42" s="1"/>
-      <c r="FL42" s="1"/>
-      <c r="FM42" s="1"/>
-      <c r="FN42" s="1"/>
-      <c r="FO42" s="1"/>
-      <c r="FP42" s="1"/>
-      <c r="FQ42" s="1"/>
-      <c r="FR42" s="1"/>
-      <c r="FS42" s="1"/>
-      <c r="FT42" s="1"/>
-      <c r="FU42" s="1"/>
-      <c r="FV42" s="1"/>
-      <c r="FW42" s="1"/>
-      <c r="FX42" s="1"/>
-      <c r="FY42" s="1"/>
-      <c r="FZ42" s="1"/>
-      <c r="GA42" s="1"/>
-      <c r="GB42" s="1"/>
-      <c r="GC42" s="1"/>
-      <c r="GD42" s="1"/>
-      <c r="GE42" s="1"/>
-      <c r="GF42" s="1"/>
-      <c r="GG42" s="1"/>
-      <c r="GH42" s="1"/>
-      <c r="GI42" s="1"/>
-      <c r="GJ42" s="1"/>
-      <c r="GK42" s="1"/>
-      <c r="GL42" s="1"/>
-      <c r="GM42" s="1"/>
-      <c r="GN42" s="1"/>
-      <c r="GO42" s="1"/>
-      <c r="GP42" s="1"/>
-      <c r="GQ42" s="1"/>
-      <c r="GR42" s="1"/>
-      <c r="GS42" s="1"/>
-      <c r="GT42" s="1"/>
-      <c r="GU42" s="1"/>
-      <c r="GV42" s="1"/>
-      <c r="GW42" s="1"/>
-      <c r="GX42" s="1"/>
-      <c r="GY42" s="1"/>
-      <c r="GZ42" s="1"/>
-      <c r="HA42" s="1"/>
-      <c r="HB42" s="1"/>
-      <c r="HC42" s="1"/>
-      <c r="HD42" s="1"/>
-      <c r="HE42" s="1"/>
-      <c r="HF42" s="1"/>
-      <c r="HG42" s="1"/>
-      <c r="HH42" s="1"/>
-      <c r="HI42" s="1"/>
-      <c r="HJ42" s="1"/>
-      <c r="HK42" s="1"/>
-      <c r="HL42" s="1"/>
-      <c r="HM42" s="1"/>
-      <c r="HN42" s="1"/>
-      <c r="HO42" s="1"/>
-      <c r="HP42" s="1"/>
-      <c r="HQ42" s="1"/>
-      <c r="HR42" s="1"/>
-      <c r="HS42" s="1"/>
-      <c r="HT42" s="1"/>
-      <c r="HU42" s="1"/>
-    </row>
-    <row r="43" s="3" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1"/>
-      <c r="B43" s="86" t="s">
-        <v>50</v>
-      </c>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="85"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-      <c r="X43" s="1"/>
-      <c r="Y43" s="1"/>
-      <c r="Z43" s="1"/>
-      <c r="AA43" s="1"/>
-      <c r="AB43" s="1"/>
-      <c r="AC43" s="1"/>
-      <c r="AD43" s="1"/>
-      <c r="AE43" s="1"/>
-      <c r="AF43" s="1"/>
-      <c r="AG43" s="1"/>
-      <c r="AH43" s="1"/>
-      <c r="AI43" s="1"/>
-      <c r="AJ43" s="1"/>
-      <c r="AK43" s="1"/>
-      <c r="AL43" s="1"/>
-      <c r="AM43" s="1"/>
-      <c r="AN43" s="1"/>
-      <c r="AO43" s="1"/>
-      <c r="AP43" s="1"/>
-      <c r="AQ43" s="1"/>
-      <c r="AR43" s="1"/>
-      <c r="AS43" s="1"/>
-      <c r="AT43" s="1"/>
-      <c r="AU43" s="1"/>
-      <c r="AV43" s="1"/>
-      <c r="AW43" s="1"/>
-      <c r="AX43" s="1"/>
-      <c r="AY43" s="1"/>
-      <c r="AZ43" s="1"/>
-      <c r="BA43" s="1"/>
-      <c r="BB43" s="1"/>
-      <c r="BC43" s="1"/>
-      <c r="BD43" s="1"/>
-      <c r="BE43" s="1"/>
-      <c r="BF43" s="1"/>
-      <c r="BG43" s="1"/>
-      <c r="BH43" s="1"/>
-      <c r="BI43" s="1"/>
-      <c r="BJ43" s="1"/>
-      <c r="BK43" s="1"/>
-      <c r="BL43" s="1"/>
-      <c r="BM43" s="1"/>
-      <c r="BN43" s="1"/>
-      <c r="BO43" s="1"/>
-      <c r="BP43" s="1"/>
-      <c r="BQ43" s="1"/>
-      <c r="BR43" s="1"/>
-      <c r="BS43" s="1"/>
-      <c r="BT43" s="1"/>
-      <c r="BU43" s="1"/>
-      <c r="BV43" s="1"/>
-      <c r="BW43" s="1"/>
-      <c r="BX43" s="1"/>
-      <c r="BY43" s="1"/>
-      <c r="BZ43" s="1"/>
-      <c r="CA43" s="1"/>
-      <c r="CB43" s="1"/>
-      <c r="CC43" s="1"/>
-      <c r="CD43" s="1"/>
-      <c r="CE43" s="1"/>
-      <c r="CF43" s="1"/>
-      <c r="CG43" s="1"/>
-      <c r="CH43" s="1"/>
-      <c r="CI43" s="1"/>
-      <c r="CJ43" s="1"/>
-      <c r="CK43" s="1"/>
-      <c r="CL43" s="1"/>
-      <c r="CM43" s="1"/>
-      <c r="CN43" s="1"/>
-      <c r="CO43" s="1"/>
-      <c r="CP43" s="1"/>
-      <c r="CQ43" s="1"/>
-      <c r="CR43" s="1"/>
-      <c r="CS43" s="1"/>
-      <c r="CT43" s="1"/>
-      <c r="CU43" s="1"/>
-      <c r="CV43" s="1"/>
-      <c r="CW43" s="1"/>
-      <c r="CX43" s="1"/>
-      <c r="CY43" s="1"/>
-      <c r="CZ43" s="1"/>
-      <c r="DA43" s="1"/>
-      <c r="DB43" s="1"/>
-      <c r="DC43" s="1"/>
-      <c r="DD43" s="1"/>
-      <c r="DE43" s="1"/>
-      <c r="DF43" s="1"/>
-      <c r="DG43" s="1"/>
-      <c r="DH43" s="1"/>
-      <c r="DI43" s="1"/>
-      <c r="DJ43" s="1"/>
-      <c r="DK43" s="1"/>
-      <c r="DL43" s="1"/>
-      <c r="DM43" s="1"/>
-      <c r="DN43" s="1"/>
-      <c r="DO43" s="1"/>
-      <c r="DP43" s="1"/>
-      <c r="DQ43" s="1"/>
-      <c r="DR43" s="1"/>
-      <c r="DS43" s="1"/>
-      <c r="DT43" s="1"/>
-      <c r="DU43" s="1"/>
-      <c r="DV43" s="1"/>
-      <c r="DW43" s="1"/>
-      <c r="DX43" s="1"/>
-      <c r="DY43" s="1"/>
-      <c r="DZ43" s="1"/>
-      <c r="EA43" s="1"/>
-      <c r="EB43" s="1"/>
-      <c r="EC43" s="1"/>
-      <c r="ED43" s="1"/>
-      <c r="EE43" s="1"/>
-      <c r="EF43" s="1"/>
-      <c r="EG43" s="1"/>
-      <c r="EH43" s="1"/>
-      <c r="EI43" s="1"/>
-      <c r="EJ43" s="1"/>
-      <c r="EK43" s="1"/>
-      <c r="EL43" s="1"/>
-      <c r="EM43" s="1"/>
-      <c r="EN43" s="1"/>
-      <c r="EO43" s="1"/>
-      <c r="EP43" s="1"/>
-      <c r="EQ43" s="1"/>
-      <c r="ER43" s="1"/>
-      <c r="ES43" s="1"/>
-      <c r="ET43" s="1"/>
-      <c r="EU43" s="1"/>
-      <c r="EV43" s="1"/>
-      <c r="EW43" s="1"/>
-      <c r="EX43" s="1"/>
-      <c r="EY43" s="1"/>
-      <c r="EZ43" s="1"/>
-      <c r="FA43" s="1"/>
-      <c r="FB43" s="1"/>
-      <c r="FC43" s="1"/>
-      <c r="FD43" s="1"/>
-      <c r="FE43" s="1"/>
-      <c r="FF43" s="1"/>
-      <c r="FG43" s="1"/>
-      <c r="FH43" s="1"/>
-      <c r="FI43" s="1"/>
-      <c r="FJ43" s="1"/>
-      <c r="FK43" s="1"/>
-      <c r="FL43" s="1"/>
-      <c r="FM43" s="1"/>
-      <c r="FN43" s="1"/>
-      <c r="FO43" s="1"/>
-      <c r="FP43" s="1"/>
-      <c r="FQ43" s="1"/>
-      <c r="FR43" s="1"/>
-      <c r="FS43" s="1"/>
-      <c r="FT43" s="1"/>
-      <c r="FU43" s="1"/>
-      <c r="FV43" s="1"/>
-      <c r="FW43" s="1"/>
-      <c r="FX43" s="1"/>
-      <c r="FY43" s="1"/>
-      <c r="FZ43" s="1"/>
-      <c r="GA43" s="1"/>
-      <c r="GB43" s="1"/>
-      <c r="GC43" s="1"/>
-      <c r="GD43" s="1"/>
-      <c r="GE43" s="1"/>
-      <c r="GF43" s="1"/>
-      <c r="GG43" s="1"/>
-      <c r="GH43" s="1"/>
-      <c r="GI43" s="1"/>
-      <c r="GJ43" s="1"/>
-      <c r="GK43" s="1"/>
-      <c r="GL43" s="1"/>
-      <c r="GM43" s="1"/>
-      <c r="GN43" s="1"/>
-      <c r="GO43" s="1"/>
-      <c r="GP43" s="1"/>
-      <c r="GQ43" s="1"/>
-      <c r="GR43" s="1"/>
-      <c r="GS43" s="1"/>
-      <c r="GT43" s="1"/>
-      <c r="GU43" s="1"/>
-      <c r="GV43" s="1"/>
-      <c r="GW43" s="1"/>
-      <c r="GX43" s="1"/>
-      <c r="GY43" s="1"/>
-      <c r="GZ43" s="1"/>
-      <c r="HA43" s="1"/>
-      <c r="HB43" s="1"/>
-      <c r="HC43" s="1"/>
-      <c r="HD43" s="1"/>
-      <c r="HE43" s="1"/>
-      <c r="HF43" s="1"/>
-      <c r="HG43" s="1"/>
-      <c r="HH43" s="1"/>
-      <c r="HI43" s="1"/>
-      <c r="HJ43" s="1"/>
-      <c r="HK43" s="1"/>
-      <c r="HL43" s="1"/>
-      <c r="HM43" s="1"/>
-      <c r="HN43" s="1"/>
-      <c r="HO43" s="1"/>
-      <c r="HP43" s="1"/>
-      <c r="HQ43" s="1"/>
-      <c r="HR43" s="1"/>
-      <c r="HS43" s="1"/>
-      <c r="HT43" s="1"/>
-      <c r="HU43" s="1"/>
-    </row>
-    <row r="44" s="3" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1"/>
-      <c r="B44" s="87"/>
-      <c r="C44" s="88"/>
-      <c r="D44" s="89"/>
-      <c r="E44" s="89"/>
-      <c r="F44" s="90"/>
-      <c r="G44" s="91"/>
-      <c r="H44" s="92"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
-      <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
-      <c r="AB44" s="1"/>
-      <c r="AC44" s="1"/>
-      <c r="AD44" s="1"/>
-      <c r="AE44" s="1"/>
-      <c r="AF44" s="1"/>
-      <c r="AG44" s="1"/>
-      <c r="AH44" s="1"/>
-      <c r="AI44" s="1"/>
-      <c r="AJ44" s="1"/>
-      <c r="AK44" s="1"/>
-      <c r="AL44" s="1"/>
-      <c r="AM44" s="1"/>
-      <c r="AN44" s="1"/>
-      <c r="AO44" s="1"/>
-      <c r="AP44" s="1"/>
-      <c r="AQ44" s="1"/>
-      <c r="AR44" s="1"/>
-      <c r="AS44" s="1"/>
-      <c r="AT44" s="1"/>
-      <c r="AU44" s="1"/>
-      <c r="AV44" s="1"/>
-      <c r="AW44" s="1"/>
-      <c r="AX44" s="1"/>
-      <c r="AY44" s="1"/>
-      <c r="AZ44" s="1"/>
-      <c r="BA44" s="1"/>
-      <c r="BB44" s="1"/>
-      <c r="BC44" s="1"/>
-      <c r="BD44" s="1"/>
-      <c r="BE44" s="1"/>
-      <c r="BF44" s="1"/>
-      <c r="BG44" s="1"/>
-      <c r="BH44" s="1"/>
-      <c r="BI44" s="1"/>
-      <c r="BJ44" s="1"/>
-      <c r="BK44" s="1"/>
-      <c r="BL44" s="1"/>
-      <c r="BM44" s="1"/>
-      <c r="BN44" s="1"/>
-      <c r="BO44" s="1"/>
-      <c r="BP44" s="1"/>
-      <c r="BQ44" s="1"/>
-      <c r="BR44" s="1"/>
-      <c r="BS44" s="1"/>
-      <c r="BT44" s="1"/>
-      <c r="BU44" s="1"/>
-      <c r="BV44" s="1"/>
-      <c r="BW44" s="1"/>
-      <c r="BX44" s="1"/>
-      <c r="BY44" s="1"/>
-      <c r="BZ44" s="1"/>
-      <c r="CA44" s="1"/>
-      <c r="CB44" s="1"/>
-      <c r="CC44" s="1"/>
-      <c r="CD44" s="1"/>
-      <c r="CE44" s="1"/>
-      <c r="CF44" s="1"/>
-      <c r="CG44" s="1"/>
-      <c r="CH44" s="1"/>
-      <c r="CI44" s="1"/>
-      <c r="CJ44" s="1"/>
-      <c r="CK44" s="1"/>
-      <c r="CL44" s="1"/>
-      <c r="CM44" s="1"/>
-      <c r="CN44" s="1"/>
-      <c r="CO44" s="1"/>
-      <c r="CP44" s="1"/>
-      <c r="CQ44" s="1"/>
-      <c r="CR44" s="1"/>
-      <c r="CS44" s="1"/>
-      <c r="CT44" s="1"/>
-      <c r="CU44" s="1"/>
-      <c r="CV44" s="1"/>
-      <c r="CW44" s="1"/>
-      <c r="CX44" s="1"/>
-      <c r="CY44" s="1"/>
-      <c r="CZ44" s="1"/>
-      <c r="DA44" s="1"/>
-      <c r="DB44" s="1"/>
-      <c r="DC44" s="1"/>
-      <c r="DD44" s="1"/>
-      <c r="DE44" s="1"/>
-      <c r="DF44" s="1"/>
-      <c r="DG44" s="1"/>
-      <c r="DH44" s="1"/>
-      <c r="DI44" s="1"/>
-      <c r="DJ44" s="1"/>
-      <c r="DK44" s="1"/>
-      <c r="DL44" s="1"/>
-      <c r="DM44" s="1"/>
-      <c r="DN44" s="1"/>
-      <c r="DO44" s="1"/>
-      <c r="DP44" s="1"/>
-      <c r="DQ44" s="1"/>
-      <c r="DR44" s="1"/>
-      <c r="DS44" s="1"/>
-      <c r="DT44" s="1"/>
-      <c r="DU44" s="1"/>
-      <c r="DV44" s="1"/>
-      <c r="DW44" s="1"/>
-      <c r="DX44" s="1"/>
-      <c r="DY44" s="1"/>
-      <c r="DZ44" s="1"/>
-      <c r="EA44" s="1"/>
-      <c r="EB44" s="1"/>
-      <c r="EC44" s="1"/>
-      <c r="ED44" s="1"/>
-      <c r="EE44" s="1"/>
-      <c r="EF44" s="1"/>
-      <c r="EG44" s="1"/>
-      <c r="EH44" s="1"/>
-      <c r="EI44" s="1"/>
-      <c r="EJ44" s="1"/>
-      <c r="EK44" s="1"/>
-      <c r="EL44" s="1"/>
-      <c r="EM44" s="1"/>
-      <c r="EN44" s="1"/>
-      <c r="EO44" s="1"/>
-      <c r="EP44" s="1"/>
-      <c r="EQ44" s="1"/>
-      <c r="ER44" s="1"/>
-      <c r="ES44" s="1"/>
-      <c r="ET44" s="1"/>
-      <c r="EU44" s="1"/>
-      <c r="EV44" s="1"/>
-      <c r="EW44" s="1"/>
-      <c r="EX44" s="1"/>
-      <c r="EY44" s="1"/>
-      <c r="EZ44" s="1"/>
-      <c r="FA44" s="1"/>
-      <c r="FB44" s="1"/>
-      <c r="FC44" s="1"/>
-      <c r="FD44" s="1"/>
-      <c r="FE44" s="1"/>
-      <c r="FF44" s="1"/>
-      <c r="FG44" s="1"/>
-      <c r="FH44" s="1"/>
-      <c r="FI44" s="1"/>
-      <c r="FJ44" s="1"/>
-      <c r="FK44" s="1"/>
-      <c r="FL44" s="1"/>
-      <c r="FM44" s="1"/>
-      <c r="FN44" s="1"/>
-      <c r="FO44" s="1"/>
-      <c r="FP44" s="1"/>
-      <c r="FQ44" s="1"/>
-      <c r="FR44" s="1"/>
-      <c r="FS44" s="1"/>
-      <c r="FT44" s="1"/>
-      <c r="FU44" s="1"/>
-      <c r="FV44" s="1"/>
-      <c r="FW44" s="1"/>
-      <c r="FX44" s="1"/>
-      <c r="FY44" s="1"/>
-      <c r="FZ44" s="1"/>
-      <c r="GA44" s="1"/>
-      <c r="GB44" s="1"/>
-      <c r="GC44" s="1"/>
-      <c r="GD44" s="1"/>
-      <c r="GE44" s="1"/>
-      <c r="GF44" s="1"/>
-      <c r="GG44" s="1"/>
-      <c r="GH44" s="1"/>
-      <c r="GI44" s="1"/>
-      <c r="GJ44" s="1"/>
-      <c r="GK44" s="1"/>
-      <c r="GL44" s="1"/>
-      <c r="GM44" s="1"/>
-      <c r="GN44" s="1"/>
-      <c r="GO44" s="1"/>
-      <c r="GP44" s="1"/>
-      <c r="GQ44" s="1"/>
-      <c r="GR44" s="1"/>
-      <c r="GS44" s="1"/>
-      <c r="GT44" s="1"/>
-      <c r="GU44" s="1"/>
-      <c r="GV44" s="1"/>
-      <c r="GW44" s="1"/>
-      <c r="GX44" s="1"/>
-      <c r="GY44" s="1"/>
-      <c r="GZ44" s="1"/>
-      <c r="HA44" s="1"/>
-      <c r="HB44" s="1"/>
-      <c r="HC44" s="1"/>
-      <c r="HD44" s="1"/>
-      <c r="HE44" s="1"/>
-      <c r="HF44" s="1"/>
-      <c r="HG44" s="1"/>
-      <c r="HH44" s="1"/>
-      <c r="HI44" s="1"/>
-      <c r="HJ44" s="1"/>
-      <c r="HK44" s="1"/>
-      <c r="HL44" s="1"/>
-      <c r="HM44" s="1"/>
-      <c r="HN44" s="1"/>
-      <c r="HO44" s="1"/>
-      <c r="HP44" s="1"/>
-      <c r="HQ44" s="1"/>
-      <c r="HR44" s="1"/>
-      <c r="HS44" s="1"/>
-      <c r="HT44" s="1"/>
-      <c r="HU44" s="1"/>
-    </row>
     <row r="1048575" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="4">
